--- a/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
+++ b/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
@@ -193,7 +193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -271,11 +271,44 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -420,6 +453,7 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -880,6 +914,7 @@
           <t>Figures below are the raw Sales Invoice amounts posted in ERPNext for the Q4 2025 period, grouped by ERPNext Customer and calendar month. This is the pre-adjustment revenue extract used to populate the Finance ledger view; downstream reconciliations (credit / debit notes, marketing-attribution reclassifications, deferred-revenue true-ups) are tracked in separate workpapers and are not netted here.</t>
         </is>
       </c>
+      <c r="B18" s="52" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2260,19 +2295,24 @@
           <t>40 clients</t>
         </is>
       </c>
-      <c r="C45" s="47" t="n">
-        <v>519050</v>
-      </c>
-      <c r="D45" s="47" t="n">
-        <v>525600</v>
-      </c>
-      <c r="E45" s="47" t="n">
-        <v>545950</v>
-      </c>
-      <c r="F45" s="47" t="n">
-        <v>1590600</v>
-      </c>
-      <c r="G45" s="48" t="n">
+      <c r="C45" s="47">
+        <f>SUM(C5:C44)</f>
+        <v>519583</v>
+      </c>
+      <c r="D45" s="47">
+        <f>SUM(D5:D44)</f>
+        <v>526133</v>
+      </c>
+      <c r="E45" s="47">
+        <f>SUM(E5:E44)</f>
+        <v>548184</v>
+      </c>
+      <c r="F45" s="47">
+        <f>SUM(F5:F44)</f>
+        <v>1593900</v>
+      </c>
+      <c r="G45" s="48">
+        <f>SUM(G5:G44)</f>
         <v>145</v>
       </c>
       <c r="H45" s="46" t="inlineStr">

--- a/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
+++ b/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
@@ -2434,6 +2434,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="72" customHeight="1">
       <c r="A13" s="51" t="inlineStr">
         <is>
@@ -2442,10 +2443,11 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Only three Bramwell-origin clients (CUST-2025-0142 Ashford, CUST-2025-0157 Northlake, CUST-2025-0198 Fenwick) appear in this Q4 2025 billing export because they migrated to Thornfield ERPNext Sales Invoice billing on or after the 09/01/2025 close. The other 17 Bramwell-origin clients enumerated in Bramwell_FY2025_standalone.xlsx are billed on legacy Bramwell systems through Q4 2025 and their Q4 revenue is captured in that standalone workbook rather than here.</t>
-        </is>
-      </c>
-    </row>
+          <t>Six Bramwell-origin clients (CUST-2025-0142 Ashford, CUST-2025-0157 Northlake, CUST-2025-0198 Fenwick, CUST-2025-0151 Ingleton, CUST-2025-0163 Larchfield, CUST-2025-0169 Norbury) appear in this Q4 2025 billing export because they migrated to Thornfield ERPNext Sales Invoice billing on or after the 09/01/2025 close. Of these, Ashford, Northlake, and Fenwick are also enumerated in Bramwell_FY2025_standalone.xlsx; Ingleton, Larchfield, and Norbury were transitioned to Thornfield invoicing but were not part of Bramwell's standalone financial-reporting scope. The remaining Bramwell-origin clients enumerated in Bramwell_FY2025_standalone.xlsx (17 of its 20 rows) are billed on legacy Bramwell systems through Q4 2025 and their Q4 revenue is captured in that standalone workbook rather than here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="51" t="inlineStr">
         <is>

--- a/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
+++ b/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
@@ -2434,8 +2434,7 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13" ht="72" customHeight="1">
+    <row r="13" ht="130" customHeight="1">
       <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Bramwell client coverage</t>
@@ -2447,7 +2446,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="51" t="inlineStr">
         <is>

--- a/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
+++ b/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H21" s="39" t="inlineStr">
         <is>
-          <t>Fixed monthly retainer of $15,360 per Master Services Agreement (Sales Order SO-2024-0261); independent of managed spend volume. Regulated (diagnostics) client.</t>
+          <t>Fixed monthly retainer of $15,360 per Master Services Agreement on file with Legal (ERPNext Sales Order SO-2024-0261); independent of managed spend volume. Regulated (diagnostics) client.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H39" s="39" t="inlineStr">
         <is>
-          <t>Inherited account; legacy MSA retainer (SO-2025-0417)</t>
+          <t>Inherited account; legacy MSA retainer (ERPNext Sales Order SO-2025-0417; agreement filed in /Legal/Legacy_Bramwell/)</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Billed on a fixed monthly retainer of $15,360 per the executed MSA (SO-2024-0261); this figure is independent of the managed spend recorded in the platform-level Q4 managed-spend export.</t>
+          <t>Billed on a fixed monthly retainer of $15,360 per the Master Services Agreement on file with Legal (ERPNext Sales Order SO-2024-0261); this figure is independent of the managed spend recorded in the platform-level Q4 managed-spend export.</t>
         </is>
       </c>
     </row>

--- a/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
+++ b/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="_-$* #,##0_-;-$* #,##0_-;_-$* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_($* #,##0_);_($* (#,##0);_($* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,6 +133,23 @@
       <b val="1"/>
       <color rgb="000F172A"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E40AF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E40AF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="11">
@@ -308,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -454,6 +471,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -777,14 +803,14 @@
     </row>
     <row r="2" ht="10" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>227 Alexander Drive, Suite 400, Durham, NC 27709</t>
         </is>
@@ -955,7 +981,7 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc. — USD, raw Sales Invoice figures (pre-adjustment)</t>
         </is>
@@ -2408,7 +2434,7 @@
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>Alan Rutherford, Finance Director — Thornfield Life Sciences Marketing, Inc.</t>
         </is>
@@ -2434,6 +2460,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="130" customHeight="1">
       <c r="A13" s="51" t="inlineStr">
         <is>
@@ -2446,6 +2473,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="51" t="inlineStr">
         <is>
